--- a/extenbooks/S602_extenbook.xlsx
+++ b/extenbooks/S602_extenbook.xlsx
@@ -11316,7 +11316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A99"/>
+  <dimension ref="A1:A98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -11355,494 +11355,491 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Status:** ingested  **Year range (book):** 1947-2011</t>
+          <t>***Status**: book_period_validated</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Corrected vs Conventional Corporate Profitability</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Corrected vs Conventional Corporate Profitability</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>## Why It Matters</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>## Why It Matters</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Fig 6.2/6.6 source. Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Fig 6.2/6.6 source. Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>## Sources (per subseries)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>## Sources (per subseries)</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>| Subseries | Appendix Table | Variable | Source agency | Notes |</t>
+          <t>|-----------|---------------|----------|---------------|-------|</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>|-----------|---------------|----------|---------------|-------|</t>
+          <t>| S602-A | II7 | `Rcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>| S602-A | II7 | `Rcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S602-B | II7 | `Rcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>| S602-B | II7 | `Rcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S602-C | II7 | `rcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>| S602-C | II7 | `rcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S602-D | II7 | `rcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>| S602-D | II7 | `rcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S602-E | II7 | `Profshcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>| S602-E | II7 | `Profshcorp` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
+          <t>| S602-F | II7 | `Profshcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>| S602-F | II7 | `Profshcorpnipa` | BEA NIPA / BEA FA / IRS SOI / Census | identity |</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>The canonical Shaikh-published values are transcribed from `SalvagedInputs/book_data/ShaikhChoppedTables/Appendix6_Table68*.xlsx` (Appendix 6.8). Upstream agencies are BEA (NIPA / Fixed Asset Accounts), IRS SOI, U.S. Census Bureau Historical Statistics 1975 (IRS book values), and FRB G.17. All public domain.</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Six lines plotted in Fig 6.2 / 6.6: corrected vs NIPA maximum rate (Rcorp vs Rcorpnipa), corrected vs NIPA average rate (rcorp vs rcorpnipa), corrected vs NIPA profit share (Profshcorp vs Profshcorpnipa). Eq. 6.10 applied with KTC(-1) = KGC(-1) + INV(-1) (uses AS004 + AS009 denominators).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Six lines plotted in Fig 6.2 / 6.6: corrected vs NIPA maximum rate (Rcorp vs Rcorpnipa), corrected vs NIPA average rate (rcorp vs rcorpnipa), corrected vs NIPA profit share (Profshcorp vs Profshcorpnipa). Eq. 6.10 applied with KTC(-1) = KGC(-1) + INV(-1) (uses AS004 + AS009 denominators).</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>## Year Coverage</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>## Year Coverage</t>
-        </is>
-      </c>
+      <c r="A34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Book period: 1947-2011. Vintage-stable extension recipe in `S602_EPR.md`.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Book period: 1947-2011. Vintage-stable extension recipe in `S602_EPR.md`.</t>
-        </is>
-      </c>
+      <c r="A36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>## Units</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>## Units</t>
-        </is>
-      </c>
+      <c r="A38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>decimal_rate_and_share</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>decimal_rate_and_share</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>## Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>## Caveats</t>
-        </is>
-      </c>
+      <c r="A42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>* Vintage-drift exposure: BEA / NIPA comprehensive revisions in 2013 and 2018 alter historical values; document vintage_year at fetch time.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>* Vintage-drift exposure: BEA / NIPA comprehensive revisions in 2013 and 2018 alter historical values; document vintage_year at fetch time.</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>## Cross-references</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>`AS003`, `AS004`, `AS009`</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>`AS003`, `AS004`, `AS009`</t>
-        </is>
-      </c>
+      <c r="A48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>## Validation Expectation</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>## Validation Expectation</t>
-        </is>
-      </c>
+      <c r="A50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>`V03_S602_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4">
+    <row r="54">
+      <c r="A54" s="4">
         <f>== EPR: S602_EPR.md ===</f>
         <v/>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t># S602 — Corrected vs Conventional Corporate Profitability (Extension Provenance Record)</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t># S602 — Corrected vs Conventional Corporate Profitability (Extension Provenance Record)</t>
-        </is>
-      </c>
+      <c r="A56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
-        </is>
-      </c>
+      <c r="A58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>## Method</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
+      <c r="A60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S602 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S602 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t>3. Re-run the construction formula end-to-end.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
+          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
+          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
+          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>## Worked Example</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>## Worked Example</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>For S602, the Phase 5 round-trip validation reads `S602_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>For S602, the Phase 5 round-trip validation reads `S602_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
-        </is>
-      </c>
+      <c r="A73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>## No-Proxy Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>## No-Proxy Disclosure</t>
-        </is>
-      </c>
+      <c r="A75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>## No-Synthetic Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>## No-Synthetic Disclosure</t>
-        </is>
-      </c>
+      <c r="A79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>## Failure Mode Table</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>## Failure Mode Table</t>
-        </is>
-      </c>
+      <c r="A83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Response |</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Response |</t>
+          <t>|---------|-----------|----------|</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>|---------|-----------|----------|</t>
+          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>## CD2 Divergence Pre-Disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
-        </is>
-      </c>
+      <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>## Anti-Degradation Compliance</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>## Anti-Degradation Compliance</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A98" t="inlineStr">
         <is>
           <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
         </is>
@@ -12359,11 +12356,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12386,76 +12383,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Corrected vs Conventional Corporate Profitability</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S602_research.json", "adequacy_report": "Technical/docs/chapters/CH6_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S602_DPR.md", "epr": "Technical/docs/series/S602_EPR.md", "loader": "Technical/code/L01_loaders/L01_S602_load.py", "processor": "Technical/code/P02_processors/P02_S602_construct.py", "validator": "Technical/code/V03_validators/V03_S602_validate.py", "processed": "Technical/data/processed/S602.parquet", "chopped_csv": "Technical/chopped/S602.csv", "extenbook_xlsx": "Technical/extenbooks/S602_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T22:43:17.420354+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S602_extenbook.xlsx
+++ b/extenbooks/S602_extenbook.xlsx
@@ -752,7 +752,7 @@
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3526,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3641,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5113,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5435,7 +5435,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5458,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5642,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5849,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6056,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6125,7 +6125,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6355,7 +6355,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6608,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -6999,7 +6999,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7367,7 +7367,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7689,7 +7689,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8034,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8264,7 +8264,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>decimal_rate</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8724,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8770,7 +8770,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -8977,7 +8977,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9115,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9345,7 +9345,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9368,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9506,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9552,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9575,7 +9575,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9621,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9690,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9713,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9736,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9805,7 +9805,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9897,7 +9897,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -9989,7 +9989,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10081,7 +10081,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10127,7 +10127,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10219,7 +10219,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10265,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10357,7 +10357,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10380,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10449,7 +10449,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10541,7 +10541,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10748,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10840,7 +10840,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10932,7 +10932,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11116,7 +11116,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11208,7 +11208,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11277,7 +11277,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11300,7 +11300,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>ratio</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A98"/>
+  <dimension ref="A1:A120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -11392,7 +11392,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fig 6.2/6.6 source. Source: Appendix Table 6.8.II.7. See `CH6_GPIM_SUMMARY.md` for the full Ch6 construction pipeline.</t>
+          <t>Source figures: Fig 6.2 / 6.6. The book-period values are transcribed verbatim from Shaikh's published Appendix 6.8 (sub-table II.7). See `CH6_GPIM_SUMMARY.md` for the full Chapter 6 construction pipeline.</t>
         </is>
       </c>
     </row>
@@ -11491,7 +11491,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Six lines plotted in Fig 6.2 / 6.6: corrected vs NIPA maximum rate (Rcorp vs Rcorpnipa), corrected vs NIPA average rate (rcorp vs rcorpnipa), corrected vs NIPA profit share (Profshcorp vs Profshcorpnipa). Eq. 6.10 applied with KTC(-1) = KGC(-1) + INV(-1) (uses AS004 + AS009 denominators).</t>
+          <t>Six lines plotted in Fig 6.2 / 6.6: corrected vs NIPA (National Income and Product Accounts) maximum rate (Rcorp vs Rcorpnipa), corrected vs NIPA average rate (rcorp vs rcorpnipa), and corrected vs NIPA profit share (Profshcorp vs Profshcorpnipa). Shaikh's eq. 6.10 is applied with the lagged total capital stock KTC[t-1] = KGC[t-1] + INV[t-1]. The linked components XS004 and XS009 (appendix "extra series" holding the GPIM capital-stock and inventory internals used in the denominators) are recorded as **documentary lineage** per Decision 0015 — they disclose the construction chain, not a live computation wired into this package; the book-period values are transcribed verbatim from Appendix 6.8.</t>
         </is>
       </c>
     </row>
@@ -11531,7 +11531,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>decimal_rate_and_share</t>
+          <t>Units differ by subseries (per-subseries units are authoritative): the four rate lines (Rcorp, Rcorpnipa, rcorp, rcorpnipa) are profit rates expressed as decimals; the two profit-share lines (Profshcorp, Profshcorpnipa) are shares expressed as decimals.</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>`AS003`, `AS004`, `AS009`</t>
+          <t>`XS003`, `XS004`, `XS009`</t>
         </is>
       </c>
     </row>
@@ -11591,95 +11591,95 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>`V03_S602_validate.py` round-trip-validates against the Appendix 6.8 source workbook at 1.0% tolerance. Per the Phase 4 adequacy report (`CH6_ADEQUACY_REPORT.json`), Phase 5 blockers B2 (NIPA T7.11 FISIM remap, resolver in `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+          <t>`V03_S602` (the validate script) round-trip-checks the built series against the Appendix 6.8 source workbook at 1.0% tolerance. Per the readiness (adequacy) review (`CH6_ADEQUACY_REPORT.json`), the two ingestion blockers B2 (a National Income and Product Accounts table 7.11 FISIM re-mapping, handled by `_nipa_t711_line_resolver.py`) and B3 (BEA 1993 depreciation rates, staged at `Reconstructed/BEA_1993_FA_methodology/`) are RESOLVED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4">
+      <c r="A54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>- **Subseries (S602-A, -B, …)** — the individual data lines that make up series S602; each suffix letter is one curve in the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>- **GPIM** — the corrected capital-stock-and-surplus construction Shaikh uses across Chapter 6 (his integrated measure of the profit rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>- **NIPA / BEA / FA** — US National Income and Product Accounts / Bureau of Economic Analysis / its Fixed Asset accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>- **XS004 / XS009** — appendix "extra series" recording GPIM construction internals; here they are documentary lineage (see Construction), not a live computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the load / process / validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset, retained for cross-checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4">
         <f>== EPR: S602_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t># S602 — Corrected vs Conventional Corporate Profitability (Extension Provenance Record)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>## Method</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S602 values**. Instead, the extension re-fetches the underlying NIPA / BEA Fixed Asset / IRS / Census components and re-runs the formula end-to-end at the current vintage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
-        </is>
-      </c>
-    </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+          <t># S602 — Corrected vs Conventional Corporate Profitability (Extension Provenance Record)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>3. Re-run the construction formula end-to-end.</t>
-        </is>
-      </c>
+      <c r="A65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4. Recompute AS003 (sectoral profit rates), AS004 (KNCcorp / KGCcorp), and AS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
+          <t>**Classification:** extendable_via_component_refetch  **Tolerance for extended values:** 1.0%</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
+          <t>## Method</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>## Worked Example</t>
+          <t>Per the Ch6 GPIM construction pipeline (see `Technical/docs/chapters/CH6_GPIM_SUMMARY.md`) and the Anu Framework anti-degradation rule, **extension does NOT splice the published S602 values**. Instead, the extension re-fetches the underlying US national-accounts components (BEA National Income and Product Accounts / Fixed Asset accounts, IRS, Census) and re-runs the formula end-to-end at the current vintage.</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>For S602, the Phase 5 round-trip validation reads `S602_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+          <t>&gt; **Scope note (Decision 0015).** The shipped data covers the book period only, transcribed verbatim from Shaikh's Appendix 6.8; the linked components XS003 / XS004 / XS009 are recorded as **documentary lineage**, not a live computation wired into this package. The component-refetch-and-recompute recipe below is the *designed forward extension* method; live GPIM re-computation is on the roadmap (Phase L) and has not yet been executed.</t>
         </is>
       </c>
     </row>
@@ -11709,139 +11709,273 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>## No-Proxy Disclosure</t>
+          <t>1. Fetch BEA NIPA tables via `S00_apis.bea_table` (`BEA_API_KEY` required) using the table ids documented in the dossier `primary_source`.</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2. Fetch BEA Fixed Asset T6.1, T6.4, T6.7, T6.8 via the same client.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
+          <t>3. Re-run the construction formula end-to-end.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4. Recompute XS003 (sectoral profit rates), XS004 (KNCcorp / KGCcorp), and XS009 (KTCcorp) using the same current-vintage components. NEVER splice the published profit-rate series.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>## No-Synthetic Disclosure</t>
+          <t>5. For S603 x1: freeze at last complete NMINT year — do NOT forward-fill.</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>6. For S604: prefer iropcorpnipa as the canonical extended series; iropcorp is bounded by NMINT / IRS-inventory availability.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>## Worked Example</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>## Failure Mode Table</t>
-        </is>
-      </c>
+      <c r="A82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>For S602, the Phase 5 round-trip validation reads `S602_raw.parquet` from the Appendix 6.8 workbook and confirms bit-for-bit reproduction of the published series for the book period 1947-2011. A worked-example year (typically 2009 per book p. 842, or 2011 per Shaikh's last published vintage) verifies headline values.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>| Failure | Detection | Response |</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>|---------|-----------|----------|</t>
+          <t>## No-Proxy Disclosure</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+          <t>No proxies are used in the book period. Book period is fully sourced from primary BEA / IRS / Census; no proxies.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>| FISIM T7.11 line revision (AS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+          <t>## No-Synthetic Disclosure</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>| BEA 1993 depreciation rate not available post-2011 | AS004/AS006/AS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>No synthetic values, interpolations, or freezes are used. All values are verbatim from Shaikh's posted Appendix 6.8 chopped tables (MD5-verified per `SalvagedInputs/book_data/Reconstructed/BEA_1993_FA_methodology/README.md` for the BEA 1993 staged inputs).</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>## CD2 Divergence Pre-Disclosure</t>
-        </is>
-      </c>
+      <c r="A92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>## Failure Mode Table</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Response |</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>## Anti-Degradation Compliance</t>
+          <t>|---------|-----------|----------|</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>| Appendix workbook missing or corrupted | `_ch6_appendix_loader` raises `FileNotFoundError` or empty DataFrame | L01 returns `status: FAIL` with explicit path |</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Per Anu Framework: extension MUST re-fetch the BEA / IRS / FRB component series and re-compute the formula end-to-end. Splicing the published series is FORBIDDEN. Loader caches BEA / FRED responses per `S00_cache` with 30-day TTL (book-period values: TTL=None).</t>
+          <t>| Variable name not in workbook | `load_variables` returns empty DataFrame | L01 records 0 rows for that subseries; V03 flags as missing |</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>| BEA / IRS vintage drift during extension | EPR-documented re-fetch script logs vintage_year; V03 tolerance widens for extension rows | Documented per-year; no silent overwrite of book period |</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>| FISIM T7.11 line revision (XS003) | `_nipa_t711_line_resolver` falls back to nearest pinned vintage with logged warning | Re-mapped by stub label; vintage logged in resolver output |</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>| BEA 1993 depreciation rate not available post-2011 | XS004/XS006/XS007 freeze depreciation rate inputs at 2011-vintage projection | Documented in `BEA_1993_FA_methodology/README.md` |</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>## CD2 Divergence Pre-Disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>CD2 / RSCD round-trip parity expected within tolerance for the book period. Informational comparison against CD2 per-series CSV when available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>## Anti-Degradation Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Per the Anu Framework anti-degradation rule, the *designed* extension re-fetches the BEA / IRS / FRB component series and re-computes the formula end-to-end; splicing the published series is FORBIDDEN. (Book-period data ships as the verbatim Appendix 6.8 transcription; the recompute is the roadmap Phase L method — see the Scope note above.) The loader caches BEA / FRED responses with a 30-day time-to-live (book-period values are cached permanently).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>- **GPIM** — the corrected capital-stock-and-surplus construction Shaikh uses across Chapter 6 (his integrated measure of the profit rate).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>- **NMINT** — net monetary interest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>- **NIPA / BEA / FA / IRS / FRB** — US National Income and Product Accounts / Bureau of Economic Analysis / its Fixed Asset accounts / Internal Revenue Service / Federal Reserve Board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>- **FISIM** — financial intermediation services indirectly measured (a national-accounts imputation affecting the T7.11 interest line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>- **XS003 / XS004 / XS009** — appendix "extra series" recording GPIM construction internals; documentary lineage, not a live computation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>- **L01 / V03** — the load and validate scripts that build and check the series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset, retained for cross-checking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>- **Phase 5 / Phase L** — Anu pipeline stages: Phase 5 = ingestion (the shipped book-period build); Phase L = the roadmap live-recompute extension stage.</t>
         </is>
       </c>
     </row>
@@ -12341,7 +12475,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T23:01:58.880793+00:00</t>
+          <t>2026-07-02T06:24:49.737744+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S602_extenbook.xlsx
+++ b/extenbooks/S602_extenbook.xlsx
@@ -12475,7 +12475,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:24:49.737744+00:00</t>
+          <t>2026-07-11T03:44:25.591446+00:00</t>
         </is>
       </c>
     </row>
@@ -12490,11 +12490,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12517,6 +12517,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_6_8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Faithful reconstruction of Shaikh Figures 6.2/6.6 (Ch6). Six lines, 1947-2011, comparing Shaikh's corrected and the conventional NIPA versions of three concepts: the maximum profit rate, the average profit rate, and the profit share. Transcribed from Shaikh's Appendix 6.8 Table II-7. Construction-relevant: shows how the imputed-interest, inventory, and capital-stock corrections move profitability versus the official accounts. The registry's mixed_units string is split per subseries (rates as decimal_rate, shares as ratio).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S602_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S602_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 6.2/6.6 source. Source: Appendix Table 6.8.II.7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>per_subseries</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
